--- a/api/templates/sz_sms_stats/en.xlsx
+++ b/api/templates/sz_sms_stats/en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\sz_sms_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E024D925-7E55-4BF9-88E2-073C34C2E6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0D9703-43A4-4413-9443-2CB5AD39AF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3D95321-C7DA-440A-B60E-5C29FCA416BB}"/>
   </bookViews>
@@ -35,10 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t>Facility/Region/National</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Number of test done</t>
   </si>
@@ -55,9 +52,6 @@
     <t>Number of SMS notifications to sent to client</t>
   </si>
   <si>
-    <t>Total SMS used in theperiod</t>
-  </si>
-  <si>
     <t>Average TAT (Sample Collection - Registration)</t>
   </si>
   <si>
@@ -67,19 +61,39 @@
     <t>Average TAT (Result Date - Result sent)</t>
   </si>
   <si>
-    <t>Frequency: Weekly/Monthly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audience: TB Focal person, M&amp;E  Officers -NTCP &amp;EHLS, LIS Advisor, </t>
+    <t>SMS Stats Report</t>
+  </si>
+  <si>
+    <t>Total SMS used in the period</t>
+  </si>
+  <si>
+    <t>Sites: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>States: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Lgas: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Dates: &lt;Dates&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,20 +108,187 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,74 +603,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D2576A-CB05-4187-998F-E769F2B698BE}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-    </row>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/api/templates/sz_sms_stats/en.xlsx
+++ b/api/templates/sz_sms_stats/en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\sz_sms_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0D9703-43A4-4413-9443-2CB5AD39AF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBED2EA-BF49-4D30-82AE-D32F7C0D6911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3D95321-C7DA-440A-B60E-5C29FCA416BB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Number of test done</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Number of SMS for test results</t>
+  </si>
+  <si>
+    <t>Number of SMS for other topics (device issues, etc.)</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -603,162 +612,191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D2576A-CB05-4187-998F-E769F2B698BE}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="12"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="15"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="14" t="s">
+        <v>15</v>
+      </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="17" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="2:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="2:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="7"/>
-    </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="10"/>
+    </row>
+    <row r="23" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/api/templates/sz_sms_stats/en.xlsx
+++ b/api/templates/sz_sms_stats/en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\sz_sms_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBED2EA-BF49-4D30-82AE-D32F7C0D6911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6778A8-9B48-4868-B8A9-BACC060FD344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3D95321-C7DA-440A-B60E-5C29FCA416BB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Number of test done</t>
   </si>
@@ -46,12 +46,6 @@
     <t>Number of errors/invalids</t>
   </si>
   <si>
-    <t>Number of SMS results sent to facility</t>
-  </si>
-  <si>
-    <t>Number of SMS notifications to sent to client</t>
-  </si>
-  <si>
     <t>Average TAT (Sample Collection - Registration)</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
   </si>
   <si>
     <t>Number of SMS for other topics (device issues, etc.)</t>
-  </si>
-  <si>
-    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -612,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D2576A-CB05-4187-998F-E769F2B698BE}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
@@ -620,27 +611,27 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -683,7 +674,7 @@
     <row r="11" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -695,7 +686,7 @@
     </row>
     <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -706,97 +697,68 @@
       <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
+    <row r="15" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="14" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="2:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="2:13" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="2" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/api/templates/sz_sms_stats/en.xlsx
+++ b/api/templates/sz_sms_stats/en.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\sz_sms_stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\sz_sms_stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6778A8-9B48-4868-B8A9-BACC060FD344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3D95321-C7DA-440A-B60E-5C29FCA416BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="sms" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,12 +63,6 @@
     <t>Sites: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>States: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>Lgas: &lt;Lgas&gt;</t>
-  </si>
-  <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
@@ -77,12 +70,18 @@
   </si>
   <si>
     <t>Number of SMS for other topics (device issues, etc.)</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -293,8 +292,36 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -602,7 +629,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D2576A-CB05-4187-998F-E769F2B698BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -616,17 +643,17 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -674,7 +701,7 @@
     <row r="11" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -686,7 +713,7 @@
     </row>
     <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
